--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260817.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260817.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.19%</t>
+          <t>11.23%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>10.97%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>8.34%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>8.09%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>4.05%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>108,266</t>
+          <t>56,759</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>56,759</t>
+          <t>108,266</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1078,46 +1078,46 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>91,463</t>
+          <t>10,937</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10,937</t>
+          <t>91,463</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,83 +1129,83 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,458</t>
+          <t>29,245</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>29,245</t>
+          <t>21,458</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>26,469</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>26,469</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,39 +1217,39 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>45,227</t>
+          <t>19,909</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>19,909</t>
+          <t>45,227</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1276,46 +1276,46 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>72,174</t>
+          <t>12,752</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,752</t>
+          <t>72,174</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>132,791,105</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
